--- a/output/北塩原村_クロス集計設計.xlsx
+++ b/output/北塩原村_クロス集計設計.xlsx
@@ -2406,7 +2406,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>無記名調査のため個人単位の突合は行わない。集計値どうしを突き合わせ、アンケートの傾向が実態と整合するかを確認する。行政データは悉皆であり、回収率57.9%のアンケートより精度が高い。</t>
+          <t>無記名調査のため個人単位の突合は行わない。集計値どうしを突き合わせ、アンケートの傾向が実態と整合するかを確認する。行政データは悉皆であり、有効回答率22.1％のアンケートより精度が高い。</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>案1を基本とし、余力があれば案2を併用する。行政データは悉皆であり、回収率57.9％のアンケートより精度が高い。ヒアリングは仕様書に明示がないため、実施する場合は範囲を協議する</t>
+          <t>案1を基本とし、余力があれば案2を併用する。行政データは悉皆であり、有効回答率22.1％のアンケートより精度が高い。ヒアリングは仕様書に明示がないため、実施する場合は範囲を協議する</t>
         </is>
       </c>
     </row>

--- a/output/北塩原村_クロス集計設計.xlsx
+++ b/output/北塩原村_クロス集計設計.xlsx
@@ -793,7 +793,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>S-1 が唯一の必須協議事項</t>
+          <t>Ｓ-1 が唯一の必須協議事項</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>S-1 は第4次障がい者計画（改定対象外）の指標の測定方法に関わるため、村の判断が必要です。S-2〜S-4 は方針の確認にあたります。</t>
+          <t>Ｓ-1 は第4次障がい者計画（改定対象外）の指標の測定方法に関わるため、村の判断が必要です。Ｓ-2〜Ｓ-4 は方針の確認にあたります。</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="6" ht="116" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>S-1</t>
+          <t>Ｓ-1</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -2703,7 +2703,7 @@
     <row r="7" ht="116" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>S-2</t>
+          <t>Ｓ-2</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -2730,7 +2730,7 @@
     <row r="8" ht="116" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>S-3</t>
+          <t>Ｓ-3</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -2757,7 +2757,7 @@
     <row r="9" ht="116" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>S-4</t>
+          <t>Ｓ-4</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
